--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_o_higgins.xlsx
@@ -404,7 +404,7 @@
         <v>25.92275144410978</v>
       </c>
       <c r="D2">
-        <v>1.723086043536594</v>
+        <v>3.114037066275704</v>
       </c>
       <c r="E2">
         <v>20.31991200128331</v>
@@ -429,7 +429,7 @@
         <v>23.78689850384149</v>
       </c>
       <c r="D3">
-        <v>1.68747867621972</v>
+        <v>2.81903676261043</v>
       </c>
       <c r="E3">
         <v>22.27370826456773</v>
@@ -454,7 +454,7 @@
         <v>27.14257697587762</v>
       </c>
       <c r="D4">
-        <v>1.409731821951894</v>
+        <v>2.283475145544111</v>
       </c>
       <c r="E4">
         <v>25.61955025240936</v>
@@ -479,7 +479,7 @@
         <v>26.82859317694277</v>
       </c>
       <c r="D5">
-        <v>1.530988452166543</v>
+        <v>2.598166127292341</v>
       </c>
       <c r="E5">
         <v>23.28170782754291</v>
@@ -504,7 +504,7 @@
         <v>27.45875965754855</v>
       </c>
       <c r="D6">
-        <v>1.603459821428572</v>
+        <v>2.864805583250249</v>
       </c>
       <c r="E6">
         <v>21.49869250225061</v>
@@ -529,7 +529,7 @@
         <v>28.90229497131286</v>
       </c>
       <c r="D7">
-        <v>1.689161262737832</v>
+        <v>3.300473405736564</v>
       </c>
       <c r="E7">
         <v>19.03171953255426</v>
@@ -554,7 +554,7 @@
         <v>27.74877477093544</v>
       </c>
       <c r="D8">
-        <v>1.548461601913718</v>
+        <v>2.715070870697136</v>
       </c>
       <c r="E8">
         <v>22.37902573231915</v>
@@ -579,7 +579,7 @@
         <v>31.48148148148148</v>
       </c>
       <c r="D9">
-        <v>1.698080942428273</v>
+        <v>3.648499693815064</v>
       </c>
       <c r="E9">
         <v>17.25</v>
@@ -604,7 +604,7 @@
         <v>24.72671622212506</v>
       </c>
       <c r="D10">
-        <v>1.505595786701778</v>
+        <v>2.398531725222863</v>
       </c>
       <c r="E10">
         <v>25.0525486074619</v>
@@ -629,7 +629,7 @@
         <v>27.9373222550605</v>
       </c>
       <c r="D11">
-        <v>1.600446229361892</v>
+        <v>2.894753833736885</v>
       </c>
       <c r="E11">
         <v>21.26089642391379</v>
@@ -654,7 +654,7 @@
         <v>25.8225739275302</v>
       </c>
       <c r="D12">
-        <v>1.6760907504363</v>
+        <v>2.955076923076923</v>
       </c>
       <c r="E12">
         <v>21.19473066388418</v>
@@ -679,7 +679,7 @@
         <v>25.63724457552138</v>
       </c>
       <c r="D13">
-        <v>1.556138337977381</v>
+        <v>2.589037360239978</v>
       </c>
       <c r="E13">
         <v>23.5139467778134</v>
@@ -704,7 +704,7 @@
         <v>26.14999240929103</v>
       </c>
       <c r="D14">
-        <v>1.487411087275601</v>
+        <v>2.434220251293422</v>
       </c>
       <c r="E14">
         <v>24.56538513912215</v>
@@ -729,7 +729,7 @@
         <v>25.27049521431544</v>
       </c>
       <c r="D15">
-        <v>1.591390728476821</v>
+        <v>2.661866518969815</v>
       </c>
       <c r="E15">
         <v>23.07053411704575</v>
@@ -754,7 +754,7 @@
         <v>29.42839494440749</v>
       </c>
       <c r="D16">
-        <v>1.606074481074481</v>
+        <v>3.045510455104551</v>
       </c>
       <c r="E16">
         <v>20.23572474377746</v>
@@ -779,7 +779,7 @@
         <v>24.79771974990805</v>
       </c>
       <c r="D17">
-        <v>1.851864464498552</v>
+        <v>3.424433249370277</v>
       </c>
       <c r="E17">
         <v>18.96232610902143</v>
@@ -804,7 +804,7 @@
         <v>26.4872521246459</v>
       </c>
       <c r="D18">
-        <v>1.475479951397327</v>
+        <v>2.422052018509654</v>
       </c>
       <c r="E18">
         <v>24.60879979581018</v>
@@ -829,7 +829,7 @@
         <v>26.77287087450427</v>
       </c>
       <c r="D19">
-        <v>1.588913809676386</v>
+        <v>2.765241635687732</v>
       </c>
       <c r="E19">
         <v>22.1947194719472</v>
@@ -854,7 +854,7 @@
         <v>26.00516414607156</v>
       </c>
       <c r="D20">
-        <v>1.292183031458532</v>
+        <v>1.946159368269921</v>
       </c>
       <c r="E20">
         <v>28.9665211062591</v>
@@ -879,7 +879,7 @@
         <v>28.68623340321453</v>
       </c>
       <c r="D21">
-        <v>1.36741519350215</v>
+        <v>2.25</v>
       </c>
       <c r="E21">
         <v>25.67103935418768</v>
@@ -904,7 +904,7 @@
         <v>23.79603399433428</v>
       </c>
       <c r="D22">
-        <v>1.494272908366534</v>
+        <v>2.318778979907264</v>
       </c>
       <c r="E22">
         <v>25.83607866626734</v>
@@ -929,7 +929,7 @@
         <v>30.15975820379965</v>
       </c>
       <c r="D23">
-        <v>1.166750629722922</v>
+        <v>1.800233190827828</v>
       </c>
       <c r="E23">
         <v>29.91164845384795</v>
@@ -954,7 +954,7 @@
         <v>23.80503885095361</v>
       </c>
       <c r="D24">
-        <v>1.31404702970297</v>
+        <v>1.912201710941018</v>
       </c>
       <c r="E24">
         <v>29.69648348709721</v>
@@ -979,7 +979,7 @@
         <v>26.98185476070724</v>
       </c>
       <c r="D25">
-        <v>1.633095343400518</v>
+        <v>2.919575285214052</v>
       </c>
       <c r="E25">
         <v>21.24346115083745</v>
@@ -1004,7 +1004,7 @@
         <v>27.23958333333333</v>
       </c>
       <c r="D26">
-        <v>1.416974169741697</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="E26">
         <v>25.40458015267176</v>
@@ -1029,7 +1029,7 @@
         <v>26.63132807363577</v>
       </c>
       <c r="D27">
-        <v>1.594548551959114</v>
+        <v>2.771438332763922</v>
       </c>
       <c r="E27">
         <v>22.17536239204001</v>
@@ -1054,7 +1054,7 @@
         <v>29.37096388423822</v>
       </c>
       <c r="D28">
-        <v>1.300466562986003</v>
+        <v>2.10417715148465</v>
       </c>
       <c r="E28">
         <v>26.86587344510546</v>
@@ -1079,7 +1079,7 @@
         <v>25.61693997771056</v>
       </c>
       <c r="D29">
-        <v>1.597202797202797</v>
+        <v>2.703249408220357</v>
       </c>
       <c r="E29">
         <v>22.74930239389044</v>
@@ -1104,7 +1104,7 @@
         <v>25.36183773735228</v>
       </c>
       <c r="D30">
-        <v>1.501096272672912</v>
+        <v>2.423881557772771</v>
       </c>
       <c r="E30">
         <v>24.76091807459356</v>
@@ -1129,7 +1129,7 @@
         <v>23.79474940334129</v>
       </c>
       <c r="D31">
-        <v>1.578749058025622</v>
+        <v>2.528666264333132</v>
       </c>
       <c r="E31">
         <v>24.21098772647574</v>
@@ -1154,7 +1154,7 @@
         <v>26.06902871105681</v>
       </c>
       <c r="D32">
-        <v>1.556453529831234</v>
+        <v>2.6192</v>
       </c>
       <c r="E32">
         <v>23.24500232450024</v>
@@ -1179,7 +1179,7 @@
         <v>26.80851063829787</v>
       </c>
       <c r="D33">
-        <v>1.240998559769563</v>
+        <v>1.859712230215827</v>
       </c>
       <c r="E33">
         <v>29.77720651242502</v>
@@ -1204,7 +1204,7 @@
         <v>25.93493239011091</v>
       </c>
       <c r="D34">
-        <v>1.60626146653252</v>
+        <v>2.753195374315277</v>
       </c>
       <c r="E34">
         <v>22.38521277078886</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.92275144410978</v>
+      </c>
+      <c r="C2">
         <v>32.1126556530032</v>
-      </c>
-      <c r="C2">
-        <v>25.92275144410978</v>
       </c>
       <c r="D2">
         <v>3.114037066275704</v>
       </c>
       <c r="E2">
-        <v>20.31991200128331</v>
+        <v>16.40312884325992</v>
       </c>
       <c r="F2">
-        <v>63.27695915545676</v>
+        <v>63.27695915545677</v>
       </c>
       <c r="G2">
-        <v>16.40312884325992</v>
+        <v>20.31991200128332</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>23.78689850384149</v>
+      </c>
+      <c r="C3">
         <v>35.47310958350182</v>
-      </c>
-      <c r="C3">
-        <v>23.78689850384149</v>
       </c>
       <c r="D3">
         <v>2.81903676261043</v>
       </c>
       <c r="E3">
-        <v>22.27370826456773</v>
+        <v>14.93588929795608</v>
       </c>
       <c r="F3">
         <v>62.7904024374762</v>
       </c>
       <c r="G3">
-        <v>14.93588929795608</v>
+        <v>22.27370826456773</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.14257697587762</v>
+      </c>
+      <c r="C4">
         <v>43.79290056873897</v>
-      </c>
-      <c r="C4">
-        <v>27.14257697587762</v>
       </c>
       <c r="D4">
         <v>2.283475145544111</v>
       </c>
       <c r="E4">
+        <v>15.8788435061955</v>
+      </c>
+      <c r="F4">
+        <v>58.50160624139512</v>
+      </c>
+      <c r="G4">
         <v>25.61955025240936</v>
-      </c>
-      <c r="F4">
-        <v>58.50160624139514</v>
-      </c>
-      <c r="G4">
-        <v>15.8788435061955</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.82859317694277</v>
+      </c>
+      <c r="C5">
         <v>38.48868590408968</v>
-      </c>
-      <c r="C5">
-        <v>26.82859317694277</v>
       </c>
       <c r="D5">
         <v>2.598166127292341</v>
       </c>
       <c r="E5">
-        <v>23.28170782754291</v>
+        <v>16.22854750941817</v>
       </c>
       <c r="F5">
         <v>60.48974466303893</v>
       </c>
       <c r="G5">
-        <v>16.22854750941817</v>
+        <v>23.28170782754291</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.45875965754855</v>
+      </c>
+      <c r="C6">
         <v>34.90638268253637</v>
-      </c>
-      <c r="C6">
-        <v>27.45875965754855</v>
       </c>
       <c r="D6">
         <v>2.864805583250249</v>
       </c>
       <c r="E6">
-        <v>21.49869250225061</v>
+        <v>16.91173318472157</v>
       </c>
       <c r="F6">
         <v>61.58957431302782</v>
       </c>
       <c r="G6">
-        <v>16.91173318472157</v>
+        <v>21.49869250225061</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.90229497131286</v>
+      </c>
+      <c r="C7">
         <v>30.29868376645292</v>
-      </c>
-      <c r="C7">
-        <v>28.90229497131286</v>
       </c>
       <c r="D7">
         <v>3.300473405736564</v>
       </c>
       <c r="E7">
-        <v>19.03171953255426</v>
+        <v>18.15459628481331</v>
       </c>
       <c r="F7">
         <v>62.81368418263243</v>
       </c>
       <c r="G7">
-        <v>18.15459628481331</v>
+        <v>19.03171953255426</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.74877477093544</v>
+      </c>
+      <c r="C8">
         <v>36.83145109737907</v>
-      </c>
-      <c r="C8">
-        <v>27.74877477093544</v>
       </c>
       <c r="D8">
         <v>2.715070870697136</v>
       </c>
       <c r="E8">
-        <v>22.37902573231915</v>
+        <v>16.8603333872795</v>
       </c>
       <c r="F8">
-        <v>60.76064088040136</v>
+        <v>60.76064088040135</v>
       </c>
       <c r="G8">
-        <v>16.8603333872795</v>
+        <v>22.37902573231914</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.48148148148148</v>
+      </c>
+      <c r="C9">
         <v>27.40852635112454</v>
-      </c>
-      <c r="C9">
-        <v>31.48148148148148</v>
       </c>
       <c r="D9">
         <v>3.648499693815064</v>
       </c>
       <c r="E9">
-        <v>17.25</v>
+        <v>19.81338028169014</v>
       </c>
       <c r="F9">
         <v>62.93661971830986</v>
       </c>
       <c r="G9">
-        <v>19.81338028169014</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.72671622212506</v>
+      </c>
+      <c r="C10">
         <v>41.69217315260166</v>
-      </c>
-      <c r="C10">
-        <v>24.72671622212506</v>
       </c>
       <c r="D10">
         <v>2.398531725222863</v>
       </c>
       <c r="E10">
-        <v>25.0525486074619</v>
+        <v>14.85811875985286</v>
       </c>
       <c r="F10">
         <v>60.08933263268523</v>
       </c>
       <c r="G10">
-        <v>14.85811875985286</v>
+        <v>25.0525486074619</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.9373222550605</v>
+      </c>
+      <c r="C11">
         <v>34.54525177047901</v>
-      </c>
-      <c r="C11">
-        <v>27.9373222550605</v>
       </c>
       <c r="D11">
         <v>2.894753833736885</v>
       </c>
       <c r="E11">
-        <v>21.26089642391379</v>
+        <v>17.19404214427895</v>
       </c>
       <c r="F11">
         <v>61.54506143180726</v>
       </c>
       <c r="G11">
-        <v>17.19404214427895</v>
+        <v>21.26089642391379</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.8225739275302</v>
+      </c>
+      <c r="C12">
         <v>33.84006663890046</v>
-      </c>
-      <c r="C12">
-        <v>25.8225739275302</v>
       </c>
       <c r="D12">
         <v>2.955076923076923</v>
       </c>
       <c r="E12">
+        <v>16.17320986044085</v>
+      </c>
+      <c r="F12">
+        <v>62.63205947567496</v>
+      </c>
+      <c r="G12">
         <v>21.19473066388418</v>
-      </c>
-      <c r="F12">
-        <v>62.63205947567498</v>
-      </c>
-      <c r="G12">
-        <v>16.17320986044085</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.63724457552138</v>
+      </c>
+      <c r="C13">
         <v>38.62439435432905</v>
-      </c>
-      <c r="C13">
-        <v>25.63724457552138</v>
       </c>
       <c r="D13">
         <v>2.589037360239978</v>
       </c>
       <c r="E13">
-        <v>23.5139467778134</v>
+        <v>15.60756652773325</v>
       </c>
       <c r="F13">
         <v>60.87848669445336</v>
       </c>
       <c r="G13">
-        <v>15.60756652773325</v>
+        <v>23.5139467778134</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.14999240929103</v>
+      </c>
+      <c r="C14">
         <v>41.08091695764384</v>
-      </c>
-      <c r="C14">
-        <v>26.14999240929103</v>
       </c>
       <c r="D14">
         <v>2.434220251293422</v>
       </c>
       <c r="E14">
-        <v>24.56538513912215</v>
+        <v>15.63705687440425</v>
       </c>
       <c r="F14">
         <v>59.79755798647361</v>
       </c>
       <c r="G14">
-        <v>15.63705687440425</v>
+        <v>24.56538513912215</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.27049521431544</v>
+      </c>
+      <c r="C15">
         <v>37.56762380357886</v>
-      </c>
-      <c r="C15">
-        <v>25.27049521431544</v>
       </c>
       <c r="D15">
         <v>2.661866518969815</v>
       </c>
       <c r="E15">
-        <v>23.07053411704575</v>
+        <v>15.51878354203936</v>
       </c>
       <c r="F15">
         <v>61.4106823409149</v>
       </c>
       <c r="G15">
-        <v>15.51878354203936</v>
+        <v>23.07053411704575</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>29.42839494440749</v>
+      </c>
+      <c r="C16">
         <v>32.83521809369952</v>
-      </c>
-      <c r="C16">
-        <v>29.42839494440749</v>
       </c>
       <c r="D16">
         <v>3.045510455104551</v>
       </c>
       <c r="E16">
-        <v>20.23572474377746</v>
+        <v>18.13616398243045</v>
       </c>
       <c r="F16">
         <v>61.62811127379209</v>
       </c>
       <c r="G16">
-        <v>18.13616398243045</v>
+        <v>20.23572474377745</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>24.79771974990805</v>
+      </c>
+      <c r="C17">
         <v>29.20191246781905</v>
-      </c>
-      <c r="C17">
-        <v>24.79771974990805</v>
       </c>
       <c r="D17">
         <v>3.424433249370277</v>
       </c>
       <c r="E17">
-        <v>18.96232610902143</v>
+        <v>16.10245387784346</v>
       </c>
       <c r="F17">
         <v>64.93522001313511</v>
       </c>
       <c r="G17">
-        <v>16.10245387784346</v>
+        <v>18.96232610902143</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.4872521246459</v>
+      </c>
+      <c r="C18">
         <v>41.28730482904012</v>
-      </c>
-      <c r="C18">
-        <v>26.4872521246459</v>
       </c>
       <c r="D18">
         <v>2.422052018509654</v>
       </c>
       <c r="E18">
-        <v>24.60879979581018</v>
+        <v>15.78740698564781</v>
       </c>
       <c r="F18">
         <v>59.603793218542</v>
       </c>
       <c r="G18">
-        <v>15.78740698564781</v>
+        <v>24.60879979581018</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>26.77287087450427</v>
+      </c>
+      <c r="C19">
         <v>36.16320494723399</v>
-      </c>
-      <c r="C19">
-        <v>26.77287087450427</v>
       </c>
       <c r="D19">
         <v>2.765241635687732</v>
       </c>
       <c r="E19">
-        <v>22.1947194719472</v>
+        <v>16.43151815181518</v>
       </c>
       <c r="F19">
         <v>61.37376237623762</v>
       </c>
       <c r="G19">
-        <v>16.43151815181518</v>
+        <v>22.1947194719472</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.00516414607156</v>
+      </c>
+      <c r="C20">
         <v>51.38325341202508</v>
-      </c>
-      <c r="C20">
-        <v>26.00516414607156</v>
       </c>
       <c r="D20">
         <v>1.946159368269921</v>
       </c>
       <c r="E20">
-        <v>28.9665211062591</v>
+        <v>14.66001247660636</v>
       </c>
       <c r="F20">
         <v>56.37346641713454</v>
       </c>
       <c r="G20">
-        <v>14.66001247660636</v>
+        <v>28.9665211062591</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>28.68623340321453</v>
+      </c>
+      <c r="C21">
         <v>44.44444444444444</v>
-      </c>
-      <c r="C21">
-        <v>28.68623340321453</v>
       </c>
       <c r="D21">
         <v>2.25</v>
       </c>
       <c r="E21">
-        <v>25.67103935418768</v>
+        <v>16.56912209889001</v>
       </c>
       <c r="F21">
         <v>57.7598385469223</v>
       </c>
       <c r="G21">
-        <v>16.56912209889001</v>
+        <v>25.67103935418768</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>23.79603399433428</v>
+      </c>
+      <c r="C22">
         <v>43.12614564239293</v>
-      </c>
-      <c r="C22">
-        <v>23.79603399433428</v>
       </c>
       <c r="D22">
         <v>2.318778979907264</v>
       </c>
       <c r="E22">
-        <v>25.83607866626734</v>
+        <v>14.25576519916143</v>
       </c>
       <c r="F22">
         <v>59.90815613457123</v>
       </c>
       <c r="G22">
-        <v>14.25576519916143</v>
+        <v>25.83607866626734</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>30.15975820379965</v>
+      </c>
+      <c r="C23">
         <v>55.54835924006909</v>
-      </c>
-      <c r="C23">
-        <v>30.15975820379965</v>
       </c>
       <c r="D23">
         <v>1.800233190827828</v>
       </c>
       <c r="E23">
-        <v>29.91164845384795</v>
+        <v>16.24040920716113</v>
       </c>
       <c r="F23">
         <v>53.84794233899093</v>
       </c>
       <c r="G23">
-        <v>16.24040920716113</v>
+        <v>29.91164845384795</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>23.80503885095361</v>
+      </c>
+      <c r="C24">
         <v>52.29573816811867</v>
-      </c>
-      <c r="C24">
-        <v>23.80503885095361</v>
       </c>
       <c r="D24">
         <v>1.912201710941018</v>
       </c>
       <c r="E24">
-        <v>29.69648348709721</v>
+        <v>13.51784997994384</v>
       </c>
       <c r="F24">
         <v>56.78566653295895</v>
       </c>
       <c r="G24">
-        <v>13.51784997994384</v>
+        <v>29.69648348709721</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.98185476070724</v>
+      </c>
+      <c r="C25">
         <v>34.25155724068557</v>
-      </c>
-      <c r="C25">
-        <v>26.98185476070724</v>
       </c>
       <c r="D25">
         <v>2.919575285214052</v>
       </c>
       <c r="E25">
-        <v>21.24346115083745</v>
+        <v>16.73465470077266</v>
       </c>
       <c r="F25">
         <v>62.02188414838988</v>
       </c>
       <c r="G25">
-        <v>16.73465470077266</v>
+        <v>21.24346115083745</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.23958333333333</v>
+      </c>
+      <c r="C26">
         <v>43.33333333333334</v>
-      </c>
-      <c r="C26">
-        <v>27.23958333333333</v>
       </c>
       <c r="D26">
         <v>2.307692307692307</v>
       </c>
       <c r="E26">
+        <v>15.96946564885496</v>
+      </c>
+      <c r="F26">
+        <v>58.62595419847329</v>
+      </c>
+      <c r="G26">
         <v>25.40458015267176</v>
-      </c>
-      <c r="F26">
-        <v>58.62595419847327</v>
-      </c>
-      <c r="G26">
-        <v>15.96946564885496</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>26.63132807363577</v>
+      </c>
+      <c r="C27">
         <v>36.08234714003945</v>
-      </c>
-      <c r="C27">
-        <v>26.63132807363577</v>
       </c>
       <c r="D27">
         <v>2.771438332763922</v>
       </c>
       <c r="E27">
-        <v>22.17536239204001</v>
+        <v>16.36698823172888</v>
       </c>
       <c r="F27">
         <v>61.45764937623112</v>
       </c>
       <c r="G27">
-        <v>16.36698823172888</v>
+        <v>22.17536239204</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.37096388423822</v>
+      </c>
+      <c r="C28">
         <v>47.52451566610858</v>
-      </c>
-      <c r="C28">
-        <v>29.37096388423822</v>
       </c>
       <c r="D28">
         <v>2.10417715148465</v>
       </c>
       <c r="E28">
-        <v>26.86587344510546</v>
+        <v>16.60356949702542</v>
       </c>
       <c r="F28">
         <v>56.53055705786912</v>
       </c>
       <c r="G28">
-        <v>16.60356949702542</v>
+        <v>26.86587344510546</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>25.61693997771056</v>
+      </c>
+      <c r="C29">
         <v>36.99251711510906</v>
-      </c>
-      <c r="C29">
-        <v>25.61693997771056</v>
       </c>
       <c r="D29">
         <v>2.703249408220357</v>
       </c>
       <c r="E29">
-        <v>22.74930239389044</v>
+        <v>15.75365937239928</v>
       </c>
       <c r="F29">
         <v>61.49703823371028</v>
       </c>
       <c r="G29">
-        <v>15.75365937239928</v>
+        <v>22.74930239389044</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.36183773735228</v>
+      </c>
+      <c r="C30">
         <v>41.25614128269818</v>
-      </c>
-      <c r="C30">
-        <v>25.36183773735228</v>
       </c>
       <c r="D30">
         <v>2.423881557772771</v>
       </c>
       <c r="E30">
-        <v>24.76091807459356</v>
+        <v>15.22154925087664</v>
       </c>
       <c r="F30">
         <v>60.0175326745298</v>
       </c>
       <c r="G30">
-        <v>15.22154925087663</v>
+        <v>24.76091807459356</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.79474940334129</v>
+      </c>
+      <c r="C31">
         <v>39.54653937947494</v>
-      </c>
-      <c r="C31">
-        <v>23.79474940334129</v>
       </c>
       <c r="D31">
         <v>2.528666264333132</v>
       </c>
       <c r="E31">
-        <v>24.21098772647574</v>
+        <v>14.56750438340152</v>
       </c>
       <c r="F31">
-        <v>61.22150789012273</v>
+        <v>61.22150789012274</v>
       </c>
       <c r="G31">
-        <v>14.56750438340152</v>
+        <v>24.21098772647575</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.06902871105681</v>
+      </c>
+      <c r="C32">
         <v>38.17959682345754</v>
-      </c>
-      <c r="C32">
-        <v>26.06902871105681</v>
       </c>
       <c r="D32">
         <v>2.6192</v>
       </c>
       <c r="E32">
-        <v>23.24500232450024</v>
+        <v>15.87168758716876</v>
       </c>
       <c r="F32">
-        <v>60.88331008833102</v>
+        <v>60.88331008833101</v>
       </c>
       <c r="G32">
-        <v>15.87168758716876</v>
+        <v>23.24500232450023</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>26.80851063829787</v>
+      </c>
+      <c r="C33">
         <v>53.77176015473888</v>
-      </c>
-      <c r="C33">
-        <v>26.80851063829787</v>
       </c>
       <c r="D33">
         <v>1.859712230215827</v>
       </c>
       <c r="E33">
+        <v>14.84575835475578</v>
+      </c>
+      <c r="F33">
+        <v>55.37703513281919</v>
+      </c>
+      <c r="G33">
         <v>29.77720651242502</v>
-      </c>
-      <c r="F33">
-        <v>55.3770351328192</v>
-      </c>
-      <c r="G33">
-        <v>14.84575835475579</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>25.93493239011091</v>
+      </c>
+      <c r="C34">
         <v>36.32143251906709</v>
-      </c>
-      <c r="C34">
-        <v>25.93493239011091</v>
       </c>
       <c r="D34">
         <v>2.753195374315277</v>
       </c>
       <c r="E34">
-        <v>22.38521277078886</v>
+        <v>15.98392297561197</v>
       </c>
       <c r="F34">
         <v>61.63086425359916</v>
       </c>
       <c r="G34">
-        <v>15.98392297561197</v>
+        <v>22.38521277078886</v>
       </c>
     </row>
   </sheetData>
